--- a/data/input_test.xlsx
+++ b/data/input_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\OpenPeru\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3D43F7-2F28-4028-9B0D-C3E1B72B6198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FAE91A-FB63-4721-9927-2402807DF1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{34264BE3-1B4E-47C2-8B79-C0289C72E04D}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{34264BE3-1B4E-47C2-8B79-C0289C72E04D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2144,16 +2144,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE5609A-ED08-476F-8184-729B5DACCDAE}">
   <dimension ref="A1:F134"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>412</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>413</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>415</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1035</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1036</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1037</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1038</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1039</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1040</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1042</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1044</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1045</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1046</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1031</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1169</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1168</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1079</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1048</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1050</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1053</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1054</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1058</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1059</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1061</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1062</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1064</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1065</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1067</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1069</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1071</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1047</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1075</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1078</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1080</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1081</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1083</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1084</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1056</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1088</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1166</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1091</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1092</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1094</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1097</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1098</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1073</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1101</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1103</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1104</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1105</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1106</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1107</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1110</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1113</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1114</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1165</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1115</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1117</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1119</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1120</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1122</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1123</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1124</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1125</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1126</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1127</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1128</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1130</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1041</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1164</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1043</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1049</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1100</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1055</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1057</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1060</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1063</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1066</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1068</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1070</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1072</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1030</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1076</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1077</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1082</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1085</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1087</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1167</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1090</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1093</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1096</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1099</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1029</v>
       </c>
@@ -3991,13 +3991,13 @@
         <v>292</v>
       </c>
       <c r="E94" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F94" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1109</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1112</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1116</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1118</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1052</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1129</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1163</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1162</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1131</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1132</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1133</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1134</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1135</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1136</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1032</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1137</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1138</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1139</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1140</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1121</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1147</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1152</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1155</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1157</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1160</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1141</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1159</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>1158</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>1156</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>1154</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>1153</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>1151</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>1150</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>1149</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>1074</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1148</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>1145</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>1144</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>1143</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>1142</v>
       </c>
